--- a/invoiceandstock/dist/medicines.xlsx
+++ b/invoiceandstock/dist/medicines.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\premier\Documents\GitHub\November2025\invoiceandstock\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\premier\Documents\GitHub\Dec2025\invoiceandstock\dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166F535D-A5FD-4B29-94B2-67B7A98CF28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2932EE-A087-490D-B868-2068CC5A673C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Medicine_Name</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>Vancomycin</t>
+  </si>
+  <si>
+    <t>despreen</t>
   </si>
 </sst>
 </file>
@@ -460,13 +463,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -485,10 +488,10 @@
         <v>10.5</v>
       </c>
       <c r="C2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -499,7 +502,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -510,7 +513,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -521,7 +524,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -532,7 +535,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -543,7 +546,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -554,7 +557,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -565,7 +568,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -576,7 +579,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -587,7 +590,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -598,7 +601,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -609,7 +612,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -620,7 +623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -631,7 +634,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -642,7 +645,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -653,7 +656,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -664,7 +667,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -675,7 +678,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -686,7 +689,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -697,7 +700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -708,7 +711,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -719,7 +722,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -728,6 +731,17 @@
       </c>
       <c r="C24">
         <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25">
+        <v>300</v>
+      </c>
+      <c r="C25">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/invoiceandstock/dist/medicines.xlsx
+++ b/invoiceandstock/dist/medicines.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\premier\Documents\GitHub\Dec2025\invoiceandstock\dist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\premier\Documents\GitHub\Dec2025\invoiceandstock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2932EE-A087-490D-B868-2068CC5A673C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD35531-B2CF-4DBE-9CE8-284C7EBA44DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="45">
   <si>
     <t>Medicine_Name</t>
   </si>
@@ -31,6 +31,15 @@
     <t>Stock</t>
   </si>
   <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>Rack_Number</t>
+  </si>
+  <si>
+    <t>Actual_Price</t>
+  </si>
+  <si>
     <t>Paracetamol</t>
   </si>
   <si>
@@ -100,7 +109,52 @@
     <t>Vancomycin</t>
   </si>
   <si>
-    <t>despreen</t>
+    <t>Furosemide</t>
+  </si>
+  <si>
+    <t>40mg</t>
+  </si>
+  <si>
+    <t>R013</t>
+  </si>
+  <si>
+    <t>Warfarin</t>
+  </si>
+  <si>
+    <t>5mg</t>
+  </si>
+  <si>
+    <t>R014</t>
+  </si>
+  <si>
+    <t>Pantoprazole</t>
+  </si>
+  <si>
+    <t>R016</t>
+  </si>
+  <si>
+    <t>Citalopram</t>
+  </si>
+  <si>
+    <t>20mg</t>
+  </si>
+  <si>
+    <t>R017</t>
+  </si>
+  <si>
+    <t>Sertraline</t>
+  </si>
+  <si>
+    <t>50mg</t>
+  </si>
+  <si>
+    <t>R018</t>
+  </si>
+  <si>
+    <t>Diclofenac</t>
+  </si>
+  <si>
+    <t>R020</t>
   </si>
 </sst>
 </file>
@@ -463,13 +517,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -479,21 +538,36 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>10.5</v>
       </c>
       <c r="C2">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>25</v>
@@ -501,10 +575,16 @@
       <c r="C3">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -512,10 +592,16 @@
       <c r="C4">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>5.5</v>
@@ -523,10 +609,16 @@
       <c r="C5">
         <v>150</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>8.75</v>
@@ -534,10 +626,16 @@
       <c r="C6">
         <v>200</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>12.25</v>
@@ -545,10 +643,16 @@
       <c r="C7">
         <v>80</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>6.8</v>
@@ -556,10 +660,16 @@
       <c r="C8">
         <v>120</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>9.5</v>
@@ -567,10 +677,16 @@
       <c r="C9">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>15.2</v>
@@ -578,10 +694,16 @@
       <c r="C10">
         <v>110</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>18.75</v>
@@ -589,10 +711,16 @@
       <c r="C11">
         <v>75</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>7.3</v>
@@ -600,10 +728,16 @@
       <c r="C12">
         <v>95</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>11.4</v>
@@ -611,10 +745,16 @@
       <c r="C13">
         <v>85</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>16.899999999999999</v>
@@ -622,10 +762,16 @@
       <c r="C14">
         <v>70</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>13.6</v>
@@ -633,10 +779,16 @@
       <c r="C15">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>10.25</v>
@@ -644,10 +796,16 @@
       <c r="C16">
         <v>128</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>4.5</v>
@@ -655,10 +813,16 @@
       <c r="C17">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>14.8</v>
@@ -666,10 +830,16 @@
       <c r="C18">
         <v>60</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>22.5</v>
@@ -677,10 +847,16 @@
       <c r="C19">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>19.75</v>
@@ -688,10 +864,16 @@
       <c r="C20">
         <v>35</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20">
+        <v>19.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>25.3</v>
@@ -699,10 +881,16 @@
       <c r="C21">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>28.9</v>
@@ -710,10 +898,16 @@
       <c r="C22">
         <v>30</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>35.6</v>
@@ -721,10 +915,16 @@
       <c r="C23">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>45.2</v>
@@ -732,16 +932,131 @@
       <c r="C24">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B25">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>200</v>
+        <v>130</v>
+      </c>
+      <c r="D25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>55</v>
+      </c>
+      <c r="D26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27">
+        <v>13</v>
+      </c>
+      <c r="C27">
+        <v>88</v>
+      </c>
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>50</v>
+      </c>
+      <c r="D28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29">
+        <v>22</v>
+      </c>
+      <c r="C29">
+        <v>48</v>
+      </c>
+      <c r="D29" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>105</v>
+      </c>
+      <c r="D30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
